--- a/plantillas/47.xlsx
+++ b/plantillas/47.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="MARCA_1">Listas!$D$2:$D$2</definedName>
@@ -9245,7 +9245,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>24.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/47.xlsx
+++ b/plantillas/47.xlsx
@@ -9685,7 +9685,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/47.xlsx
+++ b/plantillas/47.xlsx
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
